--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>78</t>
+    <t>72</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.183</t>
-  </si>
-  <si>
-    <t>(0.165)</t>
-  </si>
-  <si>
-    <t>7.038</t>
-  </si>
-  <si>
-    <t>(0.854)</t>
-  </si>
-  <si>
-    <t>4.048</t>
-  </si>
-  <si>
-    <t>(1.362)</t>
-  </si>
-  <si>
-    <t>10.943</t>
-  </si>
-  <si>
-    <t>(1.996)</t>
-  </si>
-  <si>
-    <t>2.447</t>
-  </si>
-  <si>
-    <t>(0.582)</t>
-  </si>
-  <si>
-    <t>7.590</t>
-  </si>
-  <si>
-    <t>(0.861)</t>
-  </si>
-  <si>
-    <t>2.869</t>
-  </si>
-  <si>
-    <t>(0.650)</t>
-  </si>
-  <si>
-    <t>0.396</t>
-  </si>
-  <si>
-    <t>(0.083)</t>
-  </si>
-  <si>
-    <t>13.220</t>
-  </si>
-  <si>
-    <t>(2.115)</t>
-  </si>
-  <si>
-    <t>8.808</t>
-  </si>
-  <si>
-    <t>(2.185)</t>
+    <t>1.282</t>
+  </si>
+  <si>
+    <t>(0.174)</t>
+  </si>
+  <si>
+    <t>7.625</t>
+  </si>
+  <si>
+    <t>(0.891)</t>
+  </si>
+  <si>
+    <t>3.007</t>
+  </si>
+  <si>
+    <t>(0.672)</t>
+  </si>
+  <si>
+    <t>9.145</t>
+  </si>
+  <si>
+    <t>(1.473)</t>
+  </si>
+  <si>
+    <t>1.464</t>
+  </si>
+  <si>
+    <t>(0.317)</t>
+  </si>
+  <si>
+    <t>8.111</t>
+  </si>
+  <si>
+    <t>(0.905)</t>
+  </si>
+  <si>
+    <t>2.963</t>
+  </si>
+  <si>
+    <t>(0.691)</t>
+  </si>
+  <si>
+    <t>0.429</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>11.075</t>
+  </si>
+  <si>
+    <t>(1.717)</t>
+  </si>
+  <si>
+    <t>7.248</t>
+  </si>
+  <si>
+    <t>(1.335)</t>
   </si>
   <si>
     <t>38</t>
@@ -198,7 +198,7 @@
     <t>(2.292)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.235</t>
-  </si>
-  <si>
-    <t>1.304</t>
-  </si>
-  <si>
-    <t>2.237</t>
-  </si>
-  <si>
-    <t>1.317</t>
-  </si>
-  <si>
-    <t>-1.285</t>
-  </si>
-  <si>
-    <t>0.700</t>
-  </si>
-  <si>
-    <t>-0.013</t>
-  </si>
-  <si>
-    <t>0.143</t>
-  </si>
-  <si>
-    <t>0.932</t>
-  </si>
-  <si>
-    <t>1.947</t>
+    <t>0.136</t>
+  </si>
+  <si>
+    <t>0.717</t>
+  </si>
+  <si>
+    <t>3.279***</t>
+  </si>
+  <si>
+    <t>3.115</t>
+  </si>
+  <si>
+    <t>-0.303</t>
+  </si>
+  <si>
+    <t>0.178</t>
+  </si>
+  <si>
+    <t>-0.107</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>3.076</t>
+  </si>
+  <si>
+    <t>3.507</t>
   </si>
 </sst>
 </file>
